--- a/assets/graphs/graphtable.xlsx
+++ b/assets/graphs/graphtable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 School\2025~2026\Econ Club\econgraphs\assets\graphs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC85F14A-6C57-4C67-8210-FE101DD05CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5823872A-2992-4371-AE3F-504B557D40E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2962" yWindow="2962" windowWidth="17809" windowHeight="10324" xr2:uid="{DA0673EF-C297-D94C-B899-73F575C2450E}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14889" xr2:uid="{DA0673EF-C297-D94C-B899-73F575C2450E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
   <si>
     <t>Title</t>
   </si>
@@ -151,6 +151,30 @@
   </si>
   <si>
     <t>#bfa0eb</t>
+  </si>
+  <si>
+    <t>https://www.desmos.com/calculator/wdenlekcdf</t>
+  </si>
+  <si>
+    <t>IS-LM-PC Model</t>
+  </si>
+  <si>
+    <t>This graph shows the IS-LM-PC Model, now the industry standard and an improvement to the ADAS model. IS: Investments-Savings, LM: Liquidity Preference-Money Supply, PC: Philips Curve. X=rGDP, Y=RIR</t>
+  </si>
+  <si>
+    <t>Elasticity</t>
+  </si>
+  <si>
+    <t>https://www.desmos.com/calculator/tucxllvljb</t>
+  </si>
+  <si>
+    <t>This graph explores elasticity in two demand types: linear and reciprocal, along with a total revenue graph based on quantity.</t>
+  </si>
+  <si>
+    <t>Spending Multiplier</t>
+  </si>
+  <si>
+    <t>This graph intuitively shows the spending multiplier effect, with x=income and y=consumption, showing how a difference in slopes generate the effect</t>
   </si>
 </sst>
 </file>
@@ -531,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76BEC086-2962-9B43-AA92-693AEDAE1DF1}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -577,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -678,64 +702,110 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F12" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
         <v>6</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13" t="s">
         <v>13</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E13" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -744,6 +814,29 @@
         <v>28</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/assets/graphs/graphtable.xlsx
+++ b/assets/graphs/graphtable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 School\2025~2026\Econ Club\econgraphs\assets\graphs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5823872A-2992-4371-AE3F-504B557D40E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B989A9D9-A9B8-4E4E-9885-C9B1326F20FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14889" xr2:uid="{DA0673EF-C297-D94C-B899-73F575C2450E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -159,9 +159,6 @@
     <t>IS-LM-PC Model</t>
   </si>
   <si>
-    <t>This graph shows the IS-LM-PC Model, now the industry standard and an improvement to the ADAS model. IS: Investments-Savings, LM: Liquidity Preference-Money Supply, PC: Philips Curve. X=rGDP, Y=RIR</t>
-  </si>
-  <si>
     <t>Elasticity</t>
   </si>
   <si>
@@ -175,6 +172,21 @@
   </si>
   <si>
     <t>This graph intuitively shows the spending multiplier effect, with x=income and y=consumption, showing how a difference in slopes generate the effect</t>
+  </si>
+  <si>
+    <t>Black-Scholes Parameters</t>
+  </si>
+  <si>
+    <t>https://www.desmos.com/calculator/tehqcbztrn</t>
+  </si>
+  <si>
+    <t>This graph shows the relation of an European call option price with respect to S0, K, r, s, and T</t>
+  </si>
+  <si>
+    <t>interactive</t>
+  </si>
+  <si>
+    <t>This graph shows the IS-MP-PC Model, an improvement to the ADAS model and the "industry standard" for Macro</t>
   </si>
 </sst>
 </file>
@@ -555,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76BEC086-2962-9B43-AA92-693AEDAE1DF1}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -704,16 +716,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -727,7 +739,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -736,7 +748,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
@@ -805,7 +817,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -837,6 +849,29 @@
         <v>28</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/assets/graphs/graphtable.xlsx
+++ b/assets/graphs/graphtable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0 School\2025~2026\Econ Club\econgraphs\assets\graphs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B989A9D9-A9B8-4E4E-9885-C9B1326F20FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3980B59-D5C6-48DE-90CE-09720E19CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14889" xr2:uid="{DA0673EF-C297-D94C-B899-73F575C2450E}"/>
   </bookViews>
@@ -156,9 +156,6 @@
     <t>https://www.desmos.com/calculator/wdenlekcdf</t>
   </si>
   <si>
-    <t>IS-LM-PC Model</t>
-  </si>
-  <si>
     <t>Elasticity</t>
   </si>
   <si>
@@ -187,13 +184,16 @@
   </si>
   <si>
     <t>This graph shows the IS-MP-PC Model, an improvement to the ADAS model and the "industry standard" for Macro</t>
+  </si>
+  <si>
+    <t>IS-MP-PC Model</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,6 +206,14 @@
       <color rgb="FFEBB07A"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -225,16 +233,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -716,16 +727,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -739,7 +750,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -748,7 +759,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
@@ -808,16 +819,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -854,28 +865,31 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
         <v>49</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
       </c>
       <c r="C17" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
         <v>51</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{727FAE36-1BE0-410F-88C8-FC9429B76441}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
